--- a/制作開始パック/実装・検証チェックリスト.xlsx
+++ b/制作開始パック/実装・検証チェックリスト.xlsx
@@ -1070,7 +1070,7 @@
       </c>
       <c r="G9" s="27" t="inlineStr">
         <is>
-          <t>GameModeService(Gameplay)はInfra参照不可のためGameModeBootServiceアダプタで初期化枠に載せる。ActionMap名はP0-07の4Mapに対応</t>
+          <t>GameModeService(Gameplay)はInfra参照不可のためGameModeBootServiceアダプタで初期化枠に載せる。ActionMap名はP0-07の4Mapに対応 / P0.5: NotifyListenersをスナップショット走査に修正(自己解除で後続が飛ばない)+回帰テスト追加</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>.inputactionsのmetaはUnity生成(ScriptedImporter)。Rebindは SaveBindingOverridesAsJson。GameModeCatalogのActionMap名と一致</t>
+          <t>.inputactionsのmetaはUnity生成(ScriptedImporter)。Rebindは SaveBindingOverridesAsJson。GameModeCatalogのActionMap名と一致 / P0.5: InputBootServiceでBootstrapへ接続・GameMode購読でMap自動切替・Dispose接続。BootstrapRootに_inputActions(SerializeField)追加。アセットはIA_Momotaro(project-wide化推奨、テンプレInputSystem_Actionsは要削除)</t>
         </is>
       </c>
     </row>
